--- a/scoundrel_cards.xlsx
+++ b/scoundrel_cards.xlsx
@@ -121,29 +121,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.000000"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,17 +149,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,123 +651,123 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="105">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="90">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="75">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="45">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="90">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="135">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" ht="105">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" ht="75">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="90">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" ht="75">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>32</v>
       </c>
     </row>

--- a/scoundrel_cards.xlsx
+++ b/scoundrel_cards.xlsx
@@ -33,7 +33,7 @@
     <t>Backstab</t>
   </si>
   <si>
-    <t xml:space="preserve">Discard a card to deal 1 to any target at end of round.</t>
+    <t xml:space="preserve">Discard a card to deal 2 to any target at end of round.</t>
   </si>
   <si>
     <t>cardimages/pickpocket.png</t>
@@ -51,7 +51,7 @@
     <t>Stealth</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 1. Draw 2. Discard 1.</t>
+    <t xml:space="preserve">Prevent 2. Draw 2. Discard 1.</t>
   </si>
   <si>
     <t>cardimages/lockpick.png</t>
@@ -78,7 +78,7 @@
     <t>Spy</t>
   </si>
   <si>
-    <t xml:space="preserve">Gather 1. All players reveal top 2; exhaust one, discard one.</t>
+    <t xml:space="preserve">Gather 1. All players reveal top 2 cards from their deck; exhaust one, discard one.</t>
   </si>
   <si>
     <t>cardimages/scheme.png</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Throwing Knife</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1. Draw 1. If discarded: deal 1.</t>
+    <t xml:space="preserve">Deal 2. Draw 1. If discarded: Deal 2.</t>
   </si>
   <si>
     <t>cardimages/juggling_trick.png</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Risky Slash</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1+X where X = gold spent.</t>
+    <t xml:space="preserve">Deal 2+X where X = gold spent.</t>
   </si>
 </sst>
 </file>
@@ -649,6 +649,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="28.00390625"/>
+    <col bestFit="1" min="2" max="2" width="13.421875"/>
+    <col bestFit="1" min="3" max="3" width="69.28125"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15">
       <c r="A1" t="s">

--- a/scoundrel_cards.xlsx
+++ b/scoundrel_cards.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Risky Slash</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 2+X where X = gold spent.</t>
+    <t xml:space="preserve">Deal 2 + X where X = gold spent when you play this card.</t>
   </si>
 </sst>
 </file>
@@ -687,6 +687,7 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
+      <c r="D3"/>
     </row>
     <row r="4" ht="75">
       <c r="A4" t="s">
@@ -698,6 +699,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
+      <c r="D4"/>
     </row>
     <row r="5" ht="45">
       <c r="A5" t="s">
@@ -709,6 +711,7 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
+      <c r="D5"/>
     </row>
     <row r="6" ht="90">
       <c r="A6" t="s">
@@ -720,6 +723,7 @@
       <c r="C6" t="s">
         <v>17</v>
       </c>
+      <c r="D6"/>
     </row>
     <row r="7" ht="135">
       <c r="A7" t="s">
@@ -731,6 +735,7 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
+      <c r="D7"/>
     </row>
     <row r="8" ht="105">
       <c r="A8" t="s">
@@ -742,6 +747,7 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
+      <c r="D8"/>
     </row>
     <row r="9" ht="75">
       <c r="A9" t="s">
@@ -753,6 +759,7 @@
       <c r="C9" t="s">
         <v>26</v>
       </c>
+      <c r="D9"/>
     </row>
     <row r="10" ht="90">
       <c r="A10" t="s">
@@ -764,6 +771,7 @@
       <c r="C10" t="s">
         <v>29</v>
       </c>
+      <c r="D10"/>
     </row>
     <row r="11" ht="75">
       <c r="A11" t="s">
@@ -775,6 +783,7 @@
       <c r="C11" t="s">
         <v>32</v>
       </c>
+      <c r="D11"/>
     </row>
   </sheetData>
   <hyperlinks>
